--- a/regist.php_ list.php 単体テスト仕様書 ver.2.xlsx
+++ b/regist.php_ list.php 単体テスト仕様書 ver.2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="198">
   <si>
     <t>テスト区分</t>
   </si>
@@ -683,9 +683,6 @@
     <t>登録日時表示</t>
   </si>
   <si>
-    <t>画面確認</t>
-  </si>
-  <si>
     <t>登録日時が表示される</t>
   </si>
   <si>
@@ -698,46 +695,52 @@
     <t>姓表示</t>
   </si>
   <si>
-    <t>family_nameが表示される</t>
+    <t>姓にfamily_nameが表示される</t>
   </si>
   <si>
     <t>名表示</t>
   </si>
   <si>
-    <t>last_nameが表示される</t>
+    <t>名にlast_nameが表示される</t>
   </si>
   <si>
     <t>カナ姓</t>
   </si>
   <si>
-    <t>family_name_kanaが表示される</t>
+    <t>カナ（性）にfamily_name_kanaが表示される</t>
   </si>
   <si>
     <t>カナ名</t>
   </si>
   <si>
-    <t>last_name_kanaが表示される</t>
-  </si>
-  <si>
-    <t>メール</t>
-  </si>
-  <si>
-    <t>mailが表示される</t>
+    <t>カナ（名）にlast_name_kanaが表示される</t>
+  </si>
+  <si>
+    <t>メールアドレス</t>
+  </si>
+  <si>
+    <t>メールアドレスに入力したメールアドレスが表示される</t>
   </si>
   <si>
     <t>性別変換0</t>
   </si>
   <si>
-    <t>gender=0データ確認</t>
-  </si>
-  <si>
     <t>「男」と表示される</t>
   </si>
   <si>
     <t>性別変換1</t>
   </si>
   <si>
-    <t>gender=1データ確認</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録の項目の値を入力する。
+⑤性別「女」を選択する。
+⑥画面下部にある「確認する」を押下。
+⑦登録完了しましたの文字が表示される。
+⑧TOPページへ戻るを押下。
+⑨アカウント一覧をクリックする。
+⑩list.phpのアカウント一覧の画面が表示されたことを確認する。</t>
   </si>
   <si>
     <t>「女」と表示される</t>
@@ -746,39 +749,27 @@
     <t>権限変換0</t>
   </si>
   <si>
-    <t>authority=0確認</t>
-  </si>
-  <si>
     <t>「一般」と表示される</t>
   </si>
   <si>
     <t>権限変換1</t>
   </si>
   <si>
-    <t>authority=1確認</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録の項目の値を入力する。
+⑤権限「管理者」を選択する。
+⑥画面下部にある「確認する」を押下。
+⑦登録完了しましたの文字が表示される。
+⑧TOPページへ戻るを押下。
+⑨アカウント一覧をクリックする。
+⑩list.phpのアカウント一覧の画面が表示されたことを確認する。</t>
   </si>
   <si>
     <t>「管理者」と表示される</t>
   </si>
   <si>
-    <t>削除フラグ0</t>
-  </si>
-  <si>
-    <t>delete_flag=0確認</t>
-  </si>
-  <si>
-    <t>「有効」と表示される</t>
-  </si>
-  <si>
-    <t>削除フラグ1</t>
-  </si>
-  <si>
-    <t>delete_flag=1確認</t>
-  </si>
-  <si>
-    <t>「無効」と表示される</t>
-  </si>
-  <si>
     <t>登録日表示</t>
   </si>
   <si>
@@ -791,9 +782,6 @@
     <t>並び順</t>
   </si>
   <si>
-    <t>複数データ登録後表示</t>
-  </si>
-  <si>
     <t>ID降順で表示される</t>
   </si>
   <si>
@@ -809,85 +797,90 @@
     <t>各行に削除ボタンがある</t>
   </si>
   <si>
-    <t>更新リンク</t>
-  </si>
-  <si>
-    <t>ボタン確認</t>
-  </si>
-  <si>
-    <t>update.php?id=ID形式</t>
-  </si>
-  <si>
-    <t>削除リンク</t>
-  </si>
-  <si>
-    <t>delete.php?id=ID形式</t>
-  </si>
-  <si>
-    <t>HTML特殊文字</t>
-  </si>
-  <si>
-    <t>&lt;を含むデータ表示</t>
-  </si>
-  <si>
-    <t>エスケープされ表示される</t>
-  </si>
-  <si>
     <t>長い文字列</t>
   </si>
   <si>
-    <t>長文データ登録</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録の項目の値を入力する。値はすべて5文字以上
+⑤画面下部にある「確認する」を押下。
+⑥登録完了しましたの文字が表示される。
+⑦TOPページへ戻るを押下。
+⑧アカウント一覧をクリックする。
+⑨list.phpのアカウント一覧の画面が表示されたことを確認する。</t>
   </si>
   <si>
     <t>表示崩れしない</t>
   </si>
   <si>
-    <t>NULL値</t>
-  </si>
-  <si>
-    <t>NULLデータ表示</t>
-  </si>
-  <si>
-    <t>エラーにならない</t>
-  </si>
-  <si>
     <t>半角英数</t>
   </si>
   <si>
-    <t>英数字データ表示</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録の項目の値を入力する。値はカナ以外英数字で入力する。
+⑤画面下部にある「確認する」を押下。
+⑥登録完了しましたの文字が表示される。
+⑦TOPページへ戻るを押下。
+⑧アカウント一覧をクリックする。
+⑨list.phpのアカウント一覧の画面が表示されたことを確認する。</t>
+  </si>
+  <si>
+    <t>半角英数の値が正常表示される</t>
+  </si>
+  <si>
+    <t>全角文字</t>
+  </si>
+  <si>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録の項目の値を入力する。値は全角文字で入力する。
+⑤画面下部にある「確認する」を押下。
+⑥登録完了しましたの文字が表示される。
+⑦TOPページへ戻るを押下。
+⑧アカウント一覧をクリックする。
+⑨list.phpのアカウント一覧の画面が表示されたことを確認する。</t>
   </si>
   <si>
     <t>正常表示される</t>
   </si>
   <si>
-    <t>全角文字</t>
-  </si>
-  <si>
-    <t>日本語データ表示</t>
-  </si>
-  <si>
     <t>レコード数多</t>
   </si>
   <si>
-    <t>50件以上登録</t>
-  </si>
-  <si>
-    <t>正常に表示される</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録の項目の値を入力する。値を計50件以上登録する。
+⑤画面下部にある「確認する」を押下。
+⑥登録完了しましたの文字が表示される。
+⑦TOPページへ戻るを押下。
+⑧アカウント一覧をクリックする。
+⑨list.phpのアカウント一覧の画面が表示されたことを確認する。</t>
+  </si>
+  <si>
+    <t>50件以上の値が正常に表示される</t>
   </si>
   <si>
     <t>画面再読込</t>
   </si>
   <si>
-    <t>リロード実施</t>
-  </si>
-  <si>
-    <t>同じ内容が表示される</t>
-  </si>
-  <si>
-    <t>URL直打ち</t>
-  </si>
-  <si>
-    <t>URL入力</t>
+    <t>①index.htmlをエクスプローラーで表示する。
+②アカウント登録をクリックする。
+③regist.phpのアカウント登録の画面が表示されたことを確認する。
+④アカウント登録の項目の値を入力する。
+⑤画面下部にある「確認する」を押下。
+⑥登録完了しましたの文字が表示される。
+⑦TOPページへ戻るを押下。
+⑧アカウント一覧をクリックする。
+⑨list.phpのアカウント一覧の画面が表示されたことを確認する。
+⑩リロードを押下する。</t>
+  </si>
+  <si>
+    <t>リロードを実施した場合同じ内容が表示される</t>
   </si>
 </sst>
 </file>
@@ -981,7 +974,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1019,6 +1012,9 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
@@ -1241,7 +1237,7 @@
     <col customWidth="1" min="1" max="1" width="21.13"/>
     <col customWidth="1" min="3" max="3" width="18.88"/>
     <col customWidth="1" min="4" max="4" width="60.13"/>
-    <col customWidth="1" min="5" max="5" width="36.38"/>
+    <col customWidth="1" min="5" max="5" width="46.13"/>
     <col customWidth="1" min="6" max="6" width="9.13"/>
     <col customWidth="1" min="7" max="7" width="8.88"/>
     <col customWidth="1" min="8" max="8" width="8.13"/>
@@ -2770,16 +2766,22 @@
       <c r="E54" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
+      <c r="F54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="14">
+        <v>46120.0</v>
+      </c>
+      <c r="I54" s="15"/>
       <c r="J54" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="14"/>
+      <c r="A55" s="15"/>
       <c r="B55" s="6">
         <v>53.0</v>
       </c>
@@ -2792,16 +2794,24 @@
       <c r="E55" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
+      <c r="F55" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="14">
+        <v>46120.0</v>
+      </c>
+      <c r="I55" s="15"/>
       <c r="J55" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="14"/>
+      <c r="A56" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="B56" s="6">
         <v>54.0</v>
       </c>
@@ -2809,622 +2819,506 @@
         <v>150</v>
       </c>
       <c r="D56" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
+      <c r="F56" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="14">
+        <v>46120.0</v>
+      </c>
+      <c r="I56" s="15"/>
       <c r="J56" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="14"/>
+      <c r="A57" s="15"/>
       <c r="B57" s="6">
         <v>55.0</v>
       </c>
       <c r="C57" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
+      <c r="F57" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="14">
+        <v>46120.0</v>
+      </c>
+      <c r="I57" s="15"/>
       <c r="J57" s="5"/>
     </row>
     <row r="58">
-      <c r="A58" s="14"/>
+      <c r="A58" s="15"/>
       <c r="B58" s="6">
         <v>56.0</v>
       </c>
       <c r="C58" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
+      <c r="F58" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" s="14">
+        <v>46120.0</v>
+      </c>
+      <c r="I58" s="15"/>
       <c r="J58" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="14"/>
+      <c r="A59" s="15"/>
       <c r="B59" s="6">
         <v>57.0</v>
       </c>
       <c r="C59" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
+      <c r="F59" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="14">
+        <v>46120.0</v>
+      </c>
+      <c r="I59" s="15"/>
       <c r="J59" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="14"/>
+      <c r="A60" s="15"/>
       <c r="B60" s="6">
         <v>58.0</v>
       </c>
       <c r="C60" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
+      <c r="F60" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G60" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="14">
+        <v>46120.0</v>
+      </c>
+      <c r="I60" s="15"/>
       <c r="J60" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="14"/>
+      <c r="A61" s="15"/>
       <c r="B61" s="6">
         <v>59.0</v>
       </c>
       <c r="C61" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
+      <c r="F61" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="14">
+        <v>46120.0</v>
+      </c>
+      <c r="I61" s="15"/>
       <c r="J61" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="14"/>
+      <c r="A62" s="15"/>
       <c r="B62" s="6">
         <v>60.0</v>
       </c>
       <c r="C62" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E62" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
+      <c r="F62" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="14">
+        <v>46120.0</v>
+      </c>
+      <c r="I62" s="15"/>
       <c r="J62" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="14"/>
+      <c r="A63" s="15"/>
       <c r="B63" s="6">
         <v>61.0</v>
       </c>
       <c r="C63" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E63" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
+      <c r="F63" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="14">
+        <v>46120.0</v>
+      </c>
+      <c r="I63" s="15"/>
       <c r="J63" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="14"/>
+      <c r="A64" s="15"/>
       <c r="B64" s="6">
         <v>62.0</v>
       </c>
       <c r="C64" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="E64" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="15"/>
+      <c r="H64" s="15"/>
+      <c r="I64" s="15"/>
       <c r="J64" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="14"/>
+      <c r="A65" s="15"/>
       <c r="B65" s="6">
         <v>63.0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
+        <v>170</v>
+      </c>
+      <c r="F65" s="15"/>
+      <c r="G65" s="15"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
       <c r="J65" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14"/>
+      <c r="A66" s="15"/>
       <c r="B66" s="6">
         <v>64.0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="14"/>
+        <v>173</v>
+      </c>
+      <c r="F66" s="15"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
       <c r="J66" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="14"/>
+      <c r="A67" s="15"/>
       <c r="B67" s="6">
         <v>65.0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
+        <v>175</v>
+      </c>
+      <c r="F67" s="15"/>
+      <c r="G67" s="15"/>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
       <c r="J67" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="14"/>
+      <c r="A68" s="15"/>
       <c r="B68" s="6">
         <v>66.0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
+        <v>175</v>
+      </c>
+      <c r="F68" s="15"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
       <c r="J68" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="14"/>
+      <c r="A69" s="15"/>
       <c r="B69" s="6">
         <v>67.0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
+        <v>178</v>
+      </c>
+      <c r="F69" s="15"/>
+      <c r="G69" s="15"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
       <c r="J69" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="14"/>
+      <c r="A70" s="15"/>
       <c r="B70" s="6">
         <v>68.0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
+        <v>180</v>
+      </c>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
       <c r="J70" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="14"/>
+      <c r="A71" s="15"/>
       <c r="B71" s="6">
         <v>69.0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="14"/>
+        <v>182</v>
+      </c>
+      <c r="F71" s="15"/>
+      <c r="G71" s="15"/>
+      <c r="H71" s="15"/>
+      <c r="I71" s="15"/>
       <c r="J71" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="14"/>
+      <c r="A72" s="15"/>
       <c r="B72" s="6">
         <v>70.0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
+        <v>185</v>
+      </c>
+      <c r="F72" s="15"/>
+      <c r="G72" s="15"/>
+      <c r="H72" s="15"/>
+      <c r="I72" s="15"/>
       <c r="J72" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="14"/>
+      <c r="A73" s="15"/>
       <c r="B73" s="6">
         <v>71.0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
+        <v>188</v>
+      </c>
+      <c r="F73" s="15"/>
+      <c r="G73" s="15"/>
+      <c r="H73" s="15"/>
+      <c r="I73" s="15"/>
       <c r="J73" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="14"/>
+      <c r="A74" s="15"/>
       <c r="B74" s="6">
         <v>72.0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
+        <v>191</v>
+      </c>
+      <c r="F74" s="15"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="15"/>
+      <c r="I74" s="15"/>
       <c r="J74" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="14"/>
+      <c r="A75" s="5" t="s">
+        <v>139</v>
+      </c>
       <c r="B75" s="6">
         <v>73.0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D75" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E75" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="14"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="15"/>
+      <c r="H75" s="15"/>
+      <c r="I75" s="15"/>
       <c r="J75" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="14"/>
+      <c r="A76" s="15"/>
       <c r="B76" s="6">
         <v>74.0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="14"/>
+        <v>197</v>
+      </c>
+      <c r="F76" s="15"/>
+      <c r="G76" s="15"/>
+      <c r="H76" s="15"/>
+      <c r="I76" s="15"/>
       <c r="J76" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="14"/>
-      <c r="B77" s="6">
-        <v>75.0</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="14"/>
-      <c r="J77" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="14"/>
-      <c r="B78" s="6">
-        <v>76.0</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="14"/>
-      <c r="B79" s="6">
-        <v>77.0</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="14"/>
-      <c r="B80" s="6">
-        <v>78.0</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="14"/>
-      <c r="B81" s="6">
-        <v>79.0</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="14"/>
-      <c r="B82" s="6">
-        <v>80.0</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="14"/>
-      <c r="B83" s="6">
-        <v>81.0</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="14"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="14"/>
-      <c r="J84" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3434,7 +3328,7 @@
     <mergeCell ref="A51:A52"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F53">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F63">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/regist.php_ list.php 単体テスト仕様書 ver.2.xlsx
+++ b/regist.php_ list.php 単体テスト仕様書 ver.2.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="198">
   <si>
     <t>テスト区分</t>
   </si>
@@ -3046,9 +3046,15 @@
       <c r="E64" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
-      <c r="H64" s="15"/>
+      <c r="F64" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I64" s="15"/>
       <c r="J64" s="5" t="s">
         <v>16</v>
@@ -3068,9 +3074,15 @@
       <c r="E65" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
+      <c r="F65" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I65" s="15"/>
       <c r="J65" s="5" t="s">
         <v>16</v>
@@ -3090,9 +3102,15 @@
       <c r="E66" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
+      <c r="F66" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I66" s="15"/>
       <c r="J66" s="5" t="s">
         <v>16</v>
@@ -3112,9 +3130,15 @@
       <c r="E67" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
+      <c r="F67" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I67" s="15"/>
       <c r="J67" s="5" t="s">
         <v>16</v>
@@ -3134,9 +3158,15 @@
       <c r="E68" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
+      <c r="F68" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I68" s="15"/>
       <c r="J68" s="5" t="s">
         <v>16</v>
@@ -3156,9 +3186,15 @@
       <c r="E69" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
-      <c r="H69" s="15"/>
+      <c r="F69" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I69" s="15"/>
       <c r="J69" s="5" t="s">
         <v>16</v>
@@ -3178,9 +3214,15 @@
       <c r="E70" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
-      <c r="H70" s="15"/>
+      <c r="F70" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I70" s="15"/>
       <c r="J70" s="5" t="s">
         <v>16</v>
@@ -3200,9 +3242,15 @@
       <c r="E71" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
+      <c r="F71" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I71" s="15"/>
       <c r="J71" s="5" t="s">
         <v>16</v>
@@ -3222,9 +3270,15 @@
       <c r="E72" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="15"/>
+      <c r="F72" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I72" s="15"/>
       <c r="J72" s="5" t="s">
         <v>16</v>
@@ -3244,9 +3298,15 @@
       <c r="E73" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
-      <c r="H73" s="15"/>
+      <c r="F73" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I73" s="15"/>
       <c r="J73" s="5" t="s">
         <v>16</v>
@@ -3266,9 +3326,15 @@
       <c r="E74" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="15"/>
+      <c r="F74" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I74" s="15"/>
       <c r="J74" s="5" t="s">
         <v>16</v>
@@ -3290,9 +3356,15 @@
       <c r="E75" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
-      <c r="H75" s="15"/>
+      <c r="F75" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I75" s="15"/>
       <c r="J75" s="5" t="s">
         <v>16</v>
@@ -3312,9 +3384,15 @@
       <c r="E76" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
-      <c r="H76" s="15"/>
+      <c r="F76" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="14">
+        <v>46126.0</v>
+      </c>
       <c r="I76" s="15"/>
       <c r="J76" s="5" t="s">
         <v>16</v>
@@ -3328,7 +3406,7 @@
     <mergeCell ref="A51:A52"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F63">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F76">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>
